--- a/artfynd/A 50547-2025 artfynd.xlsx
+++ b/artfynd/A 50547-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136381278</v>
       </c>
       <c r="B2" t="n">
-        <v>92266</v>
+        <v>92267</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136381851</v>
       </c>
       <c r="B3" t="n">
-        <v>92266</v>
+        <v>92267</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136382182</v>
       </c>
       <c r="B4" t="n">
-        <v>93379</v>
+        <v>93380</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136382245</v>
       </c>
       <c r="B5" t="n">
-        <v>93379</v>
+        <v>93380</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136379962</v>
       </c>
       <c r="B6" t="n">
-        <v>93389</v>
+        <v>93390</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50547-2025 artfynd.xlsx
+++ b/artfynd/A 50547-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136381278</v>
       </c>
       <c r="B2" t="n">
-        <v>92267</v>
+        <v>92280</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136381851</v>
       </c>
       <c r="B3" t="n">
-        <v>92267</v>
+        <v>92280</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136382182</v>
       </c>
       <c r="B4" t="n">
-        <v>93380</v>
+        <v>93393</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136382245</v>
       </c>
       <c r="B5" t="n">
-        <v>93380</v>
+        <v>93393</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136379962</v>
       </c>
       <c r="B6" t="n">
-        <v>93390</v>
+        <v>93403</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136380640</v>
       </c>
       <c r="B7" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136380977</v>
       </c>
       <c r="B8" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136381181</v>
       </c>
       <c r="B9" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136381232</v>
       </c>
       <c r="B10" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136381467</v>
       </c>
       <c r="B11" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136380149</v>
       </c>
       <c r="B12" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136380834</v>
       </c>
       <c r="B13" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136381795</v>
       </c>
       <c r="B14" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136381211</v>
       </c>
       <c r="B15" t="n">
-        <v>78464</v>
+        <v>78477</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136380156</v>
       </c>
       <c r="B16" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136380232</v>
       </c>
       <c r="B17" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136380252</v>
       </c>
       <c r="B18" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136380305</v>
       </c>
       <c r="B19" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136380925</v>
       </c>
       <c r="B20" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136381238</v>
       </c>
       <c r="B21" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136381463</v>
       </c>
       <c r="B22" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136382062</v>
       </c>
       <c r="B23" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136381708</v>
       </c>
       <c r="B24" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136381770</v>
       </c>
       <c r="B25" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 50547-2025 artfynd.xlsx
+++ b/artfynd/A 50547-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136381278</v>
       </c>
       <c r="B2" t="n">
-        <v>92280</v>
+        <v>92281</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136381851</v>
       </c>
       <c r="B3" t="n">
-        <v>92280</v>
+        <v>92281</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136382182</v>
       </c>
       <c r="B4" t="n">
-        <v>93393</v>
+        <v>93394</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136382245</v>
       </c>
       <c r="B5" t="n">
-        <v>93393</v>
+        <v>93394</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136379962</v>
       </c>
       <c r="B6" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136380640</v>
       </c>
       <c r="B7" t="n">
-        <v>78876</v>
+        <v>78877</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136380977</v>
       </c>
       <c r="B8" t="n">
-        <v>78876</v>
+        <v>78877</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136381181</v>
       </c>
       <c r="B9" t="n">
-        <v>78876</v>
+        <v>78877</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136381232</v>
       </c>
       <c r="B10" t="n">
-        <v>78876</v>
+        <v>78877</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136381467</v>
       </c>
       <c r="B11" t="n">
-        <v>78876</v>
+        <v>78877</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136380149</v>
       </c>
       <c r="B12" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136380834</v>
       </c>
       <c r="B13" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136381795</v>
       </c>
       <c r="B14" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136381211</v>
       </c>
       <c r="B15" t="n">
-        <v>78477</v>
+        <v>78478</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136380156</v>
       </c>
       <c r="B16" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136380232</v>
       </c>
       <c r="B17" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136380252</v>
       </c>
       <c r="B18" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136380305</v>
       </c>
       <c r="B19" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136380925</v>
       </c>
       <c r="B20" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136381238</v>
       </c>
       <c r="B21" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136381463</v>
       </c>
       <c r="B22" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136382062</v>
       </c>
       <c r="B23" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136381708</v>
       </c>
       <c r="B24" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>136381770</v>
       </c>
       <c r="B25" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
